--- a/data/trans_orig/hab_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/hab_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de hábitat en 2007</t>
+          <t>Nivel de hábitat en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>692064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>694012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>686455</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>688351</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1380439</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1382363</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>959741</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>961800</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>966347</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>968393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1928139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1930193</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>676480</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>678509</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>681957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>683841</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1360395</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1362350</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>940404</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>942222</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1036614</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1038612</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1978924</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1980834</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>891482</t>
+          <t>894327</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>994954</t>
+          <t>992065</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>986472</t>
+          <t>985633</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1095733</t>
+          <t>1092946</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1906489</t>
+          <t>1907354</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2054953</t>
+          <t>2059726</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>632133</t>
+          <t>633206</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>724258</t>
+          <t>727681</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>637222</t>
+          <t>637682</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>729615</t>
+          <t>728465</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1294800</t>
+          <t>1296600</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1427229</t>
+          <t>1431455</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>906711</t>
+          <t>904658</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1016408</t>
+          <t>1014251</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>919161</t>
+          <t>916996</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1023060</t>
+          <t>1022651</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1857507</t>
+          <t>1859920</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2004766</t>
+          <t>2003939</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>646096</t>
+          <t>647647</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>742228</t>
+          <t>744615</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>644580</t>
+          <t>644124</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>740229</t>
+          <t>732873</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1323580</t>
+          <t>1313239</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1452440</t>
+          <t>1447598</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de hábitat en 2012</t>
+          <t>Nivel de hábitat en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>701468</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>703469</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>694994</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>697050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1398489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1400519</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1015861</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1017947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1030078</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1032184</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2048033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2050131</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>755515</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>757623</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>775060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>777174</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1532684</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1534797</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>945741</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>947739</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1049889</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1051901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1997634</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1999640</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>894522</t>
+          <t>892396</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1002061</t>
+          <t>1003039</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>997203</t>
+          <t>998156</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1108294</t>
+          <t>1105771</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1924914</t>
+          <t>1922939</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2082231</t>
+          <t>2077399</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>707324</t>
+          <t>708550</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>811811</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>728334</t>
+          <t>728029</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>831544</t>
+          <t>828237</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1466349</t>
+          <t>1472363</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1616328</t>
+          <t>1611174</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>964916</t>
+          <t>965434</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1072798</t>
+          <t>1075257</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>978117</t>
+          <t>976727</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1086774</t>
+          <t>1089314</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1974713</t>
+          <t>1979444</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2129050</t>
+          <t>2135967</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>657254</t>
+          <t>652940</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>758510</t>
+          <t>747822</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>648899</t>
+          <t>650224</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>748467</t>
+          <t>741690</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1327104</t>
+          <t>1337842</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1471809</t>
+          <t>1467647</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de hábitat en 2016</t>
+          <t>Nivel de hábitat en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>672816</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>674800</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>670902</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>672839</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1345677</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1347639</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1020369</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1022431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1040865</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1042913</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2063288</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2065344</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>757460</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>759552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>782966</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>785011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1542493</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1544563</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>935637</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>937567</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1041691</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1043779</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1979335</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1981346</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>886366</t>
+          <t>892546</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>990065</t>
+          <t>996320</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>988443</t>
+          <t>990568</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1101490</t>
+          <t>1102588</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1905622</t>
+          <t>1901870</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2059697</t>
+          <t>2055899</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>710620</t>
+          <t>712727</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>811491</t>
+          <t>806612</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>737407</t>
+          <t>740465</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>840294</t>
+          <t>838956</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1469428</t>
+          <t>1470679</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1613210</t>
+          <t>1613719</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>968703</t>
+          <t>967131</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1070653</t>
+          <t>1075538</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>981728</t>
+          <t>993325</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1096808</t>
+          <t>1104737</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1988472</t>
+          <t>1983360</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2152280</t>
+          <t>2143599</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>626213</t>
+          <t>627637</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>722210</t>
+          <t>719217</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>633074</t>
+          <t>626724</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>718794</t>
+          <t>718419</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1272809</t>
+          <t>1288973</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1405565</t>
+          <t>1423327</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de hábitat en 2023</t>
+          <t>Nivel de hábitat en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>633772</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>724208</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1359447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1190490</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>957438</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2149851</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>702681</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>931656</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1636221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>925064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1093587</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2020252</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>723735</t>
+          <t>703905</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1022500</t>
+          <t>1020844</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>915416</t>
+          <t>910509</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1239112</t>
+          <t>1233808</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1769496</t>
+          <t>1767072</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2211481</t>
+          <t>2199966</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>558919</t>
+          <t>548384</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>783315</t>
+          <t>783446</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>749119</t>
+          <t>751072</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1484903</t>
+          <t>1477471</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1421563</t>
+          <t>1432257</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2202958</t>
+          <t>2137860</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>998746</t>
+          <t>1002015</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1718523</t>
+          <t>1716892</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>771404</t>
+          <t>776314</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1042404</t>
+          <t>1041184</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1915933</t>
+          <t>1914634</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2759629</t>
+          <t>2719432</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>490064</t>
+          <t>506269</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>705745</t>
+          <t>708452</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>618868</t>
+          <t>612201</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>839382</t>
+          <t>843218</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1191553</t>
+          <t>1175986</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1497533</t>
+          <t>1508357</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/hab_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/hab_R-Habitat-trans_orig.xlsx
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>894327</t>
+          <t>892150</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>992065</t>
+          <t>993383</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>985633</t>
+          <t>976978</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1092946</t>
+          <t>1092184</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1907354</t>
+          <t>1908290</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2059726</t>
+          <t>2056034</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>633206</t>
+          <t>628615</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>727681</t>
+          <t>723875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>637682</t>
+          <t>642517</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>728465</t>
+          <t>731585</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1296600</t>
+          <t>1293942</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1431455</t>
+          <t>1427372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>904658</t>
+          <t>912636</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1014251</t>
+          <t>1017984</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>916996</t>
+          <t>915841</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1022651</t>
+          <t>1022475</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1859920</t>
+          <t>1857369</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2003939</t>
+          <t>2012713</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>647647</t>
+          <t>651405</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>744615</t>
+          <t>748549</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>644124</t>
+          <t>642185</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>732873</t>
+          <t>737355</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1313239</t>
+          <t>1311725</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1447598</t>
+          <t>1450793</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>892396</t>
+          <t>895254</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1003039</t>
+          <t>996010</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>998156</t>
+          <t>1000548</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1105771</t>
+          <t>1114640</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1922939</t>
+          <t>1925831</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2077399</t>
+          <t>2072685</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>708550</t>
+          <t>704247</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>811811</t>
+          <t>807042</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>728029</t>
+          <t>725253</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>828237</t>
+          <t>825261</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1472363</t>
+          <t>1460849</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1611174</t>
+          <t>1609291</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>965434</t>
+          <t>964036</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1075257</t>
+          <t>1072687</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>976727</t>
+          <t>976249</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1089314</t>
+          <t>1085287</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1979444</t>
+          <t>1971592</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2135967</t>
+          <t>2123814</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>652940</t>
+          <t>658751</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>747822</t>
+          <t>752803</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>650224</t>
+          <t>649492</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>741690</t>
+          <t>748402</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1337842</t>
+          <t>1339140</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1467647</t>
+          <t>1472729</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>892546</t>
+          <t>889213</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>996320</t>
+          <t>993565</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>990568</t>
+          <t>984906</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1102588</t>
+          <t>1100122</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1901870</t>
+          <t>1899916</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2055899</t>
+          <t>2056598</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>712727</t>
+          <t>708154</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>806612</t>
+          <t>810287</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>740465</t>
+          <t>736597</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>838956</t>
+          <t>842938</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1470679</t>
+          <t>1471172</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1613719</t>
+          <t>1625272</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>967131</t>
+          <t>967598</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1075538</t>
+          <t>1076209</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>993325</t>
+          <t>988249</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1104737</t>
+          <t>1098488</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1983360</t>
+          <t>1995835</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2143599</t>
+          <t>2141742</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>627637</t>
+          <t>630144</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>719217</t>
+          <t>721653</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>626724</t>
+          <t>626323</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>718419</t>
+          <t>716491</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1288973</t>
+          <t>1280341</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1423327</t>
+          <t>1407641</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>703905</t>
+          <t>936622</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1020844</t>
+          <t>1050725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>910509</t>
+          <t>1069779</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1233808</t>
+          <t>1169010</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1767072</t>
+          <t>2030792</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2199966</t>
+          <t>2186518</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>548384</t>
+          <t>745327</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>783446</t>
+          <t>861685</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>751072</t>
+          <t>768697</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1477471</t>
+          <t>860282</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1432257</t>
+          <t>1535558</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2137860</t>
+          <t>1685554</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1002015</t>
+          <t>989617</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1716892</t>
+          <t>1113805</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>958652</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>776314</t>
+          <t>1021756</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1041184</t>
+          <t>1118406</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1914634</t>
+          <t>2045507</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2719432</t>
+          <t>2199992</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>506269</t>
+          <t>638709</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>708452</t>
+          <t>744139</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>612201</t>
+          <t>695979</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>843218</t>
+          <t>774124</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1175986</t>
+          <t>1361993</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1508357</t>
+          <t>1490729</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
